--- a/Data/Export/Common/JobType_指令.xlsx
+++ b/Data/Export/Common/JobType_指令.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="100">
   <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -390,6 +390,21 @@
   <si>
     <t>10</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二虎竞食</t>
+  </si>
+  <si>
+    <t>计略/二虎竞食</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>流言</t>
+  </si>
+  <si>
+    <t>计略/流言</t>
   </si>
 </sst>
 </file>
@@ -1724,15 +1739,68 @@
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="B28" s="4">
+        <v>25</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="J29" s="4"/>
+      <c r="B29" s="4">
+        <v>27</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B30" s="4"/>
